--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0072.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0072.xlsx
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>("Một dấu hiệu mới vừa xuất hiện trên bản đồ... Chắc ta phải đi kiểm tra thôi.")</t>
+          <t>("Một dấu hiệu mới vừa xuất hiện trên bản đồ... Chắc tao phải đi kiểm tra thôi.")</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>{Male=Chàng trai;Female=Cô gái} trẻ, cậu có thể lần theo dấu vết của anh ấy và chụp lại những nơi anh ấy đã đi qua không?</t>
+          <t>{Male=Young man;Female=Young lady} trẻ, cậu có thể lần theo dấu vết của anh ấy và chụp lại những nơi anh ấy đã đi qua không?</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Ta trông cậy vào {Male=cậu;Female=cô} nhé.</t>
+          <t>Ta trông cậy vào {Male=young man;Female=young lady} nhé.</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Dù chỉ còn mình ta đứng vững, ta vẫn sẽ truy lùng lũ quái vật đó… và ghi lại từng dấu vết… cho Ephor…</t>
+          <t>Dù chỉ còn mình tao đứng vững, tao vẫn sẽ truy lùng lũ quái vật đó… và ghi lại từng dấu vết… cho Ephor…</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Được rồi, được rồi. Đi đi, Acis. Ta sẽ lo cho bản thân và đứa nhỏ thôi.</t>
+          <t>Được rồi, được rồi. Đi đi, Acis. Tao sẽ lo cho bản thân và đứa nhỏ thôi.</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Ngươi... Ừ, nếu đó là lựa chọn của ngươi, ta không nói thêm nữa.</t>
+          <t>Mày... Ừ, nếu đó là lựa chọn của mày, tao không nói thêm nữa.</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Tất nhiên là ta sợ chứ. Thật đấy, chân ta vẫn đang run cầm cập đây này.</t>
+          <t>Tất nhiên là tao sợ chứ. Thật đấy, chân tao vẫn đang run cầm cập đây này.</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Chỉ cần hứa với ta là cậu sẽ trở về bình an vô sự thôi, được không?</t>
+          <t>Chỉ cần hứa với tao là cậu sẽ trở về bình an vô sự thôi, được không?</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Chúng không xuất thân từ Cộng Hưởng Giả hay Somnoire... Chẳng cần phải "đặc biệt" gì cả. Chúng chỉ là những giấc mơ của những kẻ đã ngã xuống ở Septimont, không thể chạm tới Somnoire.</t>
+          <t>Chúng không xuất thân từ Resonator hay Somnoire... Chẳng cần phải "đặc biệt" gì cả. Chúng chỉ là những giấc mơ của những kẻ đã ngã xuống ở Septimont, không thể chạm tới Somnoire.</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Tch... Xin lỗi vì cách ta nói, nhưng dù sao... Ngươi đừng hòng thay đổi được ý ta về hắn!</t>
+          <t>Tch... Xin lỗi vì cách tao nói, nhưng dù sao... Mày đừng hòng thay đổi được ý tao về hắn!</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Để tôi lo.</t>
+          <t>Để đó cho ta.</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Im lặng! Ta nhìn rõ mà! Cứ la hét thế này, mấy thứ kia sẽ kéo đến đấy! Hiểu chưa?</t>
+          <t>Im lặng! Tao nhìn rõ mà! Cứ la hét thế này, mấy thứ kia sẽ kéo đến đấy! Hiểu chưa?</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Cô gái Augusta kia đã đánh bại cả trăm đấu sĩ và cướp lấy gươm của họ. Cô ta mà nhớ nổi tên một kẻ yếu đuối như ngươi sao?</t>
+          <t>Cô gái Augusta kia đã đánh bại cả trăm đấu sĩ và cướp lấy gươm của họ. Cô ta mà nhớ nổi tên một kẻ yếu đuối như mày sao?</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Thôi đi Aeolus, đừng làm Kẻ Chiến Binh nữa. Cậu không hiểu à? Là Cộng Hưởng Giả, cậu đang già đi quá nhanh đấy.</t>
+          <t>Thôi đi Aeolus, đừng làm Kẻ Chiến Binh nữa. Cậu không hiểu à? Là Resonator, cậu đang già đi quá nhanh đấy.</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Đó chính là số phận của một Võ Sĩ Giác Đấu, {Male=ngài;Female=nữ hiệp} {PlayerName}—</t>
+          <t>Đó chính là số phận của một Võ Sĩ Giác Đấu, {Male=Sir.;Female=Lady.} {PlayerName}—</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Đùa kiểu gì thế hả? Chơi khăm à? Nếu ta mắc lừa, hắn sẽ nhảy ra cười nhạo ta chắc?</t>
+          <t>Đùa kiểu gì thế hả? Chơi khăm à? Nếu tao mắc lừa, hắn sẽ nhảy ra cười nhạo tao chắc?</t>
         </is>
       </c>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Ta không biết nhiều về văn hóa của Septimont, hay về cậu. Nhưng ta tôn trọng lựa chọn của cậu.</t>
+          <t>Tao không biết nhiều về văn hóa của Septimont, hay về cậu. Nhưng tao tôn trọng lựa chọn của cậu.</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>...Ừ. Thách thức cậu cũng chẳng ích gì. Ta thậm chí còn không biết mình đang làm gì nữa...</t>
+          <t>...Ừ. Thách thức cậu cũng chẳng ích gì. Tao thậm chí còn không biết mình đang làm gì nữa...</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Không phải khoe đâu, nhưng hồi xưa tụi ta nổi tiếng khắp nơi. Cho đến khi chán ngấy bọn nhà tài trợ và quý tộc. Thế là ta bỏ đi luôn.</t>
+          <t>Không phải khoe đâu, nhưng hồi xưa tụi tao nổi tiếng khắp nơi. Cho đến khi chán ngấy bọn nhà tài trợ và quý tộc. Thế là tao bỏ đi luôn.</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Ta sẽ lo con Kerasaur. Không được để nó tới gần thêm nữa.</t>
+          <t>Tao sẽ lo con Kerasaur. Không được để nó tới gần thêm nữa.</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23194,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>…Đừng nghĩ chuyện này sẽ khiến ta cảm ơn ngươi đâu, Gren.</t>
+          <t>…Đừng nghĩ chuyện này sẽ khiến tao cảm ơn mày đâu, Gren.</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Hừ. Được rồi. Ta sẽ băng bó. Rồi chúng ta đi tiếp.</t>
+          <t>Hừ. Được rồi. Tao sẽ băng bó. Rồi chúng ta đi tiếp.</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>A, đúng là giọng nhà vô địch! Một ngón tay thôi à? Thế nghĩa là ngươi mạnh gấp năm lần Huấn Luyện Viên luôn đấy!</t>
+          <t>A, đúng là giọng nhà vô địch! Một ngón tay thôi à? Thế nghĩa là mày mạnh gấp năm lần Huấn Luyện Viên luôn đấy!</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Không. Hắn chỉ xuất hiện sau khi tụi ta dựng trại ở đây chưa được bao lâu.</t>
+          <t>Không. Hắn chỉ xuất hiện sau khi tụi tao dựng trại ở đây chưa được bao lâu.</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Tại sao?</t>
+          <t>Sao vậy?</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Pfft, ngươi có khiếu hài hước đấy nhỉ! Không ngờ đứa nhỏ tuổi như ngươi lại pha trò hay hơn cả ta. Khoan... Đừng bảo ngươi già hơn ta đấy nhé?</t>
+          <t>Pfft, mày có khiếu hài hước đấy nhỉ! Không ngờ đứa nhỏ tuổi như mày lại pha trò hay hơn cả tao. Khoan... Đừng bảo mày già hơn tao đấy nhé?</t>
         </is>
       </c>
     </row>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Ta đã hứa với Gren là sẽ để mắt tới Rolla.</t>
+          <t>Tao đã hứa với Gren là sẽ để mắt tới Rolla.</t>
         </is>
       </c>
     </row>
